--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-observation-common.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-observation-common.xlsx
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -617,7 +617,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -917,7 +917,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -969,7 +969,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1146,7 +1146,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1175,7 +1175,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1227,7 +1227,7 @@
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1257,7 +1257,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1294,7 +1294,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1369,7 +1369,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1419,7 +1419,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1452,7 +1452,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
